--- a/Manual-Testing/04_Test_Cases/Test_Cases_OrangeHRM.xlsx
+++ b/Manual-Testing/04_Test_Cases/Test_Cases_OrangeHRM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Testing\Manual\OrangeHRM_Manual_Testing_Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Testing\OrangeHRM-QA-Project\Manual-Testing\04_Test_Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4C8205-A8C7-4C64-81D1-52AA2013A63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974E3A6F-8DD0-4346-8AA1-3AE67CF8CB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{75FEA98A-859C-4F7D-ACE4-5329782BB20B}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="166">
   <si>
     <t>Test Case Description</t>
   </si>
@@ -77,13 +77,460 @@
   </si>
   <si>
     <t>Precondition</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Login</t>
+  </si>
+  <si>
+    <t>Verify login with valid username and invalid password</t>
+  </si>
+  <si>
+    <t>click login</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>TC_Login_001</t>
+  </si>
+  <si>
+    <t>TC_Login_002</t>
+  </si>
+  <si>
+    <t>TC_Login_003</t>
+  </si>
+  <si>
+    <t>TC_Login_004</t>
+  </si>
+  <si>
+    <t>TC_Login_005</t>
+  </si>
+  <si>
+    <t>TC_Login_006</t>
+  </si>
+  <si>
+    <t>TC_Login_007</t>
+  </si>
+  <si>
+    <t>TC_Login_008</t>
+  </si>
+  <si>
+    <t>Verify logout functionality</t>
+  </si>
+  <si>
+    <t>Invalid credentials error message should be  displayed.</t>
+  </si>
+  <si>
+    <t>As Expected</t>
+  </si>
+  <si>
+    <t>Enter valid username</t>
+  </si>
+  <si>
+    <t>Enter valid password</t>
+  </si>
+  <si>
+    <t>User should be successfully logged in and navigated to Dashboard page</t>
+  </si>
+  <si>
+    <t>click login button</t>
+  </si>
+  <si>
+    <t>Verify that user is able to login successfully with valid credentials</t>
+  </si>
+  <si>
+    <t>Verify Dashboard page elements</t>
+  </si>
+  <si>
+    <t>Click on Profile menu and select Logout option</t>
+  </si>
+  <si>
+    <t>Dashboard page menu, profile icon should be visible</t>
+  </si>
+  <si>
+    <t>User should be logged out and redirected to Login page</t>
+  </si>
+  <si>
+    <t>Login page should be displayed successfully</t>
+  </si>
+  <si>
+    <t>Launch the application URL in browser</t>
+  </si>
+  <si>
+    <t>Verify that user is not able to login with invalid username and valid password</t>
+  </si>
+  <si>
+    <t>Enter invalid username</t>
+  </si>
+  <si>
+    <t>Click Login button</t>
+  </si>
+  <si>
+    <t>Verify error message displayed on screen</t>
+  </si>
+  <si>
+    <t>Verify user remains on Login page</t>
+  </si>
+  <si>
+    <t>User should not be navigated to Dashboard and should remain on Login page</t>
+  </si>
+  <si>
+    <t>Invalid credentials error message should be displayed clearly and correctly</t>
+  </si>
+  <si>
+    <t>Username should be accepted and displayed in the field</t>
+  </si>
+  <si>
+    <t>https://opensource-demo.orangehrmlive.com/web/index.php/auth/login</t>
+  </si>
+  <si>
+    <t>wrongusername</t>
+  </si>
+  <si>
+    <t>Enter invalid Password</t>
+  </si>
+  <si>
+    <t>Verify error message is displayed on the screen</t>
+  </si>
+  <si>
+    <t>verify user is still on the login page</t>
+  </si>
+  <si>
+    <t>wrongpassword</t>
+  </si>
+  <si>
+    <t>Launch application Url in the browser</t>
+  </si>
+  <si>
+    <t>Leave username and password fileds empty</t>
+  </si>
+  <si>
+    <t>Login page should be displayed correctly.</t>
+  </si>
+  <si>
+    <t>both fields should remain empty</t>
+  </si>
+  <si>
+    <t>System should display "Required" message for both fields</t>
+  </si>
+  <si>
+    <t>system should trigger validation for both fields</t>
+  </si>
+  <si>
+    <t>Verify validation message for both username and password fields</t>
+  </si>
+  <si>
+    <t>User should not be logged in and should remain on Login page</t>
+  </si>
+  <si>
+    <t>Verify login with both username and password fields left empty</t>
+  </si>
+  <si>
+    <t>Verify login with valid username and empty password</t>
+  </si>
+  <si>
+    <t>Verify login with valid password and empty username</t>
+  </si>
+  <si>
+    <t>Launch application url in the browser</t>
+  </si>
+  <si>
+    <t>Leave password filed empty</t>
+  </si>
+  <si>
+    <t>verify validation message displayed for password field</t>
+  </si>
+  <si>
+    <t>verify user is still remain on login page</t>
+  </si>
+  <si>
+    <t>Login page should be opened successfully</t>
+  </si>
+  <si>
+    <t>username should be accepted and displayed in the field.</t>
+  </si>
+  <si>
+    <t>password field should remain empty</t>
+  </si>
+  <si>
+    <t>system should trigger the validation for password field</t>
+  </si>
+  <si>
+    <t>System should display "Required" message for password field</t>
+  </si>
+  <si>
+    <t>user should not be loggedin and should remain in login page</t>
+  </si>
+  <si>
+    <t>Leave username filed empty</t>
+  </si>
+  <si>
+    <t>username field should remain empty</t>
+  </si>
+  <si>
+    <t>password should be accepted and masked in the field.</t>
+  </si>
+  <si>
+    <t>system should trigger the validation for username field</t>
+  </si>
+  <si>
+    <t>System should display "Required" message for username field</t>
+  </si>
+  <si>
+    <t>verify validation message displayed for username field</t>
+  </si>
+  <si>
+    <t>verify error message for invalid credentials login</t>
+  </si>
+  <si>
+    <t>Launch the application url in browser</t>
+  </si>
+  <si>
+    <t>login page should be displayed successfully</t>
+  </si>
+  <si>
+    <t>enter invalid username</t>
+  </si>
+  <si>
+    <t>username should be accepted and displayed in the field</t>
+  </si>
+  <si>
+    <t>enter invalid password</t>
+  </si>
+  <si>
+    <t>click on login button</t>
+  </si>
+  <si>
+    <t>verify correct error message displayed for invalid credentials</t>
+  </si>
+  <si>
+    <t>application should validate and display error message</t>
+  </si>
+  <si>
+    <t>"Invalid Credentials" error message should be displayed correctly.</t>
+  </si>
+  <si>
+    <t>verify user remains on login page</t>
+  </si>
+  <si>
+    <t>click on profile dropdown menu on top right corner</t>
+  </si>
+  <si>
+    <t>Verify session complete using browser back button</t>
+  </si>
+  <si>
+    <t>verify redirection to login page url</t>
+  </si>
+  <si>
+    <t>Verify login page content</t>
+  </si>
+  <si>
+    <t>Profile dropdown menu should be displayed with available options</t>
+  </si>
+  <si>
+    <t>User should be logged out successfully</t>
+  </si>
+  <si>
+    <t>click logout from the dropdown options</t>
+  </si>
+  <si>
+    <t>User should be redirected to Login page after logout</t>
+  </si>
+  <si>
+    <t>Login page fields (Username, Password, Login button) should be visible and functional</t>
+  </si>
+  <si>
+    <t>User should not be able to access Dashboard using browser back button</t>
+  </si>
+  <si>
+    <t>Username should be accepted and displayed in username field</t>
+  </si>
+  <si>
+    <t>Password should be accepted and masked in the field</t>
+  </si>
+  <si>
+    <t>password should be accepted and masked in the field</t>
+  </si>
+  <si>
+    <t>User is logged into the application and Dashboard page is displayed</t>
+  </si>
+  <si>
+    <t>TC_Login_009</t>
+  </si>
+  <si>
+    <t>Launch the application url in the browser</t>
+  </si>
+  <si>
+    <t>click on "Forgot Your Password?" link.</t>
+  </si>
+  <si>
+    <t>Verify Reset Password page content</t>
+  </si>
+  <si>
+    <t>user should be redirected to Login page after clicking cancle.</t>
+  </si>
+  <si>
+    <t>Username field, Reset button, and Cancel button should be visible and enabled</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> User is on login page and application Url is accessible</t>
+  </si>
+  <si>
+    <t>user should be redirected "Reset Password" page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter Username </t>
+  </si>
+  <si>
+    <t>Username accepted and displayed in the field</t>
+  </si>
+  <si>
+    <t>Click Reset password button</t>
+  </si>
+  <si>
+    <t>After entering valid username and clicking Reset button, system does not display any success/error message.</t>
+  </si>
+  <si>
+    <t>System should display confirmation message indicating that password reset link has been sent to linked mail id</t>
+  </si>
+  <si>
+    <t>Verify Forgot Password Page Functionality</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>admin123</t>
+  </si>
+  <si>
+    <t>TC_PIM_001</t>
+  </si>
+  <si>
+    <t>PIM</t>
+  </si>
+  <si>
+    <t>Enter first name</t>
+  </si>
+  <si>
+    <t>enter middle name</t>
+  </si>
+  <si>
+    <t>enter last name</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>Add Employee page should be displayed</t>
+  </si>
+  <si>
+    <t>first name should be accepted</t>
+  </si>
+  <si>
+    <t>middle name should be accepted</t>
+  </si>
+  <si>
+    <t>Last name should be accepted</t>
+  </si>
+  <si>
+    <t>click save button</t>
+  </si>
+  <si>
+    <t>verify employee details page</t>
+  </si>
+  <si>
+    <t>Verify navigation after successful login</t>
+  </si>
+  <si>
+    <t>User is login page and application URL is accessible</t>
+  </si>
+  <si>
+    <t>Launch the application URL in the browser</t>
+  </si>
+  <si>
+    <t>enter valid username</t>
+  </si>
+  <si>
+    <t>enter valid password</t>
+  </si>
+  <si>
+    <t>Login page should be displayed successfully in the browser</t>
+  </si>
+  <si>
+    <t>user should redirects to navigation page after successful login</t>
+  </si>
+  <si>
+    <t>verify Url of dashboard page</t>
+  </si>
+  <si>
+    <t>URL should contain "/dashboard"</t>
+  </si>
+  <si>
+    <t>As expected</t>
+  </si>
+  <si>
+    <t>TS_LOGIN_001</t>
+  </si>
+  <si>
+    <t>TS_LOGIN_002</t>
+  </si>
+  <si>
+    <t>TS_LOGIN_003</t>
+  </si>
+  <si>
+    <t>TS_LOGIN_004</t>
+  </si>
+  <si>
+    <t>TS_LOGIN_005</t>
+  </si>
+  <si>
+    <t>TS_LOGIN_006</t>
+  </si>
+  <si>
+    <t>TS_PIM_001</t>
+  </si>
+  <si>
+    <t>Verify admin can add employee successfully</t>
+  </si>
+  <si>
+    <t>Admin logged in and on PIM page</t>
+  </si>
+  <si>
+    <t>Navigate to PIMmodule and click "Add employee" button</t>
+  </si>
+  <si>
+    <t>employee created successfully and user should be navigated to employee information page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employee Information page url should contain "/viewPersonalDetails" </t>
+  </si>
+  <si>
+    <t>verify employee name displayed correctly</t>
+  </si>
+  <si>
+    <t>Employee details should match entered data</t>
+  </si>
+  <si>
+    <t>Bug</t>
+  </si>
+  <si>
+    <t>Huntur</t>
+  </si>
+  <si>
+    <t>TC_Login_010</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,8 +562,29 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -135,8 +603,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -145,45 +625,222 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{4806A06E-8709-4DCA-AEA0-02084EEC38CC}"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -209,8 +866,8 @@
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{6EC9FCEC-8708-45BD-8079-A5AB5F2D56C5}">
-      <tableStyleElement type="wholeTable" dxfId="1"/>
-      <tableStyleElement type="headerRow" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="3"/>
+      <tableStyleElement type="headerRow" dxfId="2"/>
     </tableStyle>
   </tableStyles>
   <colors>
@@ -526,94 +1183,2114 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74709E7A-6F17-4BAA-85D6-5A1E2510EB4F}">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.85546875" customWidth="1"/>
-    <col min="12" max="12" width="22" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="32.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="32.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="30.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12" ht="32.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="B1" s="30"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+    </row>
+    <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="6" t="s">
         <v>15</v>
       </c>
     </row>
+    <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C3" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3" s="15">
+        <v>1</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="4">
+        <v>2</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="24"/>
+    </row>
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="4">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L5" s="24"/>
+    </row>
+    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="4">
+        <v>4</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L6" s="24"/>
+    </row>
+    <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="4">
+        <v>5</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L7" s="24"/>
+    </row>
+    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="4">
+        <v>6</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="28"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F10" s="11">
+        <v>1</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I10" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="24"/>
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="11">
+        <v>2</v>
+      </c>
+      <c r="G11" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L11" s="24"/>
+    </row>
+    <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="24"/>
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="4">
+        <v>3</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="24"/>
+    </row>
+    <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="24"/>
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="4">
+        <v>4</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="24"/>
+    </row>
+    <row r="14" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="4">
+        <v>5</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="24"/>
+    </row>
+    <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A15" s="25"/>
+      <c r="B15" s="25"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="4">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L15" s="25"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="27"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="26"/>
+      <c r="J16" s="26"/>
+      <c r="K16" s="26"/>
+      <c r="L16" s="26"/>
+    </row>
+    <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A17" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="4">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I18" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L18" s="24"/>
+    </row>
+    <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="24"/>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="4">
+        <v>3</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K19" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L19" s="24"/>
+    </row>
+    <row r="20" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="24"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="4">
+        <v>4</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="24"/>
+    </row>
+    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A21" s="24"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="4">
+        <v>5</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L21" s="24"/>
+    </row>
+    <row r="22" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A22" s="25"/>
+      <c r="B22" s="25"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="4">
+        <v>6</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="25"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A23" s="20"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="33"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="21"/>
+      <c r="L23" s="22"/>
+    </row>
+    <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I24" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L24" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="24"/>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="4">
+        <v>2</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="24"/>
+      <c r="B26" s="24"/>
+      <c r="C26" s="24"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="4">
+        <v>3</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L26" s="24"/>
+    </row>
+    <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="24"/>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="4">
+        <v>4</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="J27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="24"/>
+    </row>
+    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="4">
+        <v>5</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L28" s="25"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+    </row>
+    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F30" s="4">
+        <v>1</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K30" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L30" s="23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="24"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="24"/>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="4">
+        <v>2</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J31" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L31" s="24"/>
+    </row>
+    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="24"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="4">
+        <v>3</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="24"/>
+    </row>
+    <row r="33" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="24"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="4">
+        <v>4</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L33" s="24"/>
+    </row>
+    <row r="34" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A34" s="24"/>
+      <c r="B34" s="24"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="4">
+        <v>5</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L34" s="24"/>
+    </row>
+    <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="25"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="25"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="4">
+        <v>6</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I35" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L35" s="25"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="27"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+    </row>
+    <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A37" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="C37" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H37" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L37" s="23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="24"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="4">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L38" s="24"/>
+    </row>
+    <row r="39" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="4">
+        <v>3</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L39" s="24"/>
+    </row>
+    <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="4">
+        <v>4</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L40" s="24"/>
+    </row>
+    <row r="41" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="4">
+        <v>5</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I41" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="J41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K41" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L41" s="24"/>
+    </row>
+    <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="25"/>
+      <c r="B42" s="25"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="25"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="4">
+        <v>6</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L42" s="25"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="26"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26"/>
+    </row>
+    <row r="44" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A44" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C44" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F44" s="4">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="4">
+        <v>2</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K45" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="24"/>
+    </row>
+    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="24"/>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="4">
+        <v>3</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L46" s="24"/>
+    </row>
+    <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
+      <c r="C47" s="24"/>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="4">
+        <v>4</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="24"/>
+    </row>
+    <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A48" s="24"/>
+      <c r="B48" s="24"/>
+      <c r="C48" s="24"/>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="4">
+        <v>5</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L48" s="24"/>
+    </row>
+    <row r="49" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="25"/>
+      <c r="B49" s="25"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="25"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="4">
+        <v>6</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K49" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L49" s="25"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="20"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="21"/>
+      <c r="D50" s="21"/>
+      <c r="E50" s="21"/>
+      <c r="F50" s="21"/>
+      <c r="G50" s="21"/>
+      <c r="H50" s="21"/>
+      <c r="I50" s="21"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="21"/>
+      <c r="L50" s="22"/>
+    </row>
+    <row r="51" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A51" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B51" s="23" t="s">
+        <v>152</v>
+      </c>
+      <c r="C51" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F51" s="4">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H51" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I51" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L51" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="24"/>
+      <c r="B52" s="24"/>
+      <c r="C52" s="24"/>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="4">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K52" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="24"/>
+    </row>
+    <row r="53" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="24"/>
+      <c r="B53" s="24"/>
+      <c r="C53" s="24"/>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="4">
+        <v>3</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L53" s="24"/>
+    </row>
+    <row r="54" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A54" s="24"/>
+      <c r="B54" s="24"/>
+      <c r="C54" s="24"/>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="4">
+        <v>4</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L54" s="24"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="25"/>
+      <c r="B55" s="25"/>
+      <c r="C55" s="25"/>
+      <c r="D55" s="25"/>
+      <c r="E55" s="25"/>
+      <c r="F55" s="4">
+        <v>5</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I55" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="J55" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="K55" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L55" s="25"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="26"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="26"/>
+      <c r="F56" s="27"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="26"/>
+      <c r="I56" s="26"/>
+      <c r="J56" s="26"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="26"/>
+    </row>
+    <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A57" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C57" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D57" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="F57" s="4">
+        <v>1</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K57" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L57" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A58" s="24"/>
+      <c r="B58" s="24"/>
+      <c r="C58" s="24"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="24"/>
+      <c r="F58" s="4">
+        <v>2</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K58" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L58" s="24"/>
+    </row>
+    <row r="59" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A59" s="24"/>
+      <c r="B59" s="24"/>
+      <c r="C59" s="24"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="24"/>
+      <c r="F59" s="4">
+        <v>3</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K59" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L59" s="24"/>
+    </row>
+    <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A60" s="24"/>
+      <c r="B60" s="24"/>
+      <c r="C60" s="24"/>
+      <c r="D60" s="24"/>
+      <c r="E60" s="24"/>
+      <c r="F60" s="4">
+        <v>4</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L60" s="24"/>
+    </row>
+    <row r="61" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A61" s="25"/>
+      <c r="B61" s="25"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="25"/>
+      <c r="E61" s="25"/>
+      <c r="F61" s="4">
+        <v>5</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K61" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L61" s="25"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="20"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="21"/>
+      <c r="F62" s="33"/>
+      <c r="G62" s="21"/>
+      <c r="H62" s="21"/>
+      <c r="I62" s="21"/>
+      <c r="J62" s="21"/>
+      <c r="K62" s="21"/>
+      <c r="L62" s="22"/>
+    </row>
+    <row r="63" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A63" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C63" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="D63" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F63" s="4">
+        <v>1</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H63" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L63" s="23" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A64" s="24"/>
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="24"/>
+      <c r="E64" s="24"/>
+      <c r="F64" s="4">
+        <v>2</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L64" s="24"/>
+    </row>
+    <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A65" s="24"/>
+      <c r="B65" s="24"/>
+      <c r="C65" s="24"/>
+      <c r="D65" s="24"/>
+      <c r="E65" s="24"/>
+      <c r="F65" s="4">
+        <v>3</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I65" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K65" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L65" s="24"/>
+    </row>
+    <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A66" s="24"/>
+      <c r="B66" s="24"/>
+      <c r="C66" s="24"/>
+      <c r="D66" s="24"/>
+      <c r="E66" s="24"/>
+      <c r="F66" s="4">
+        <v>4</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I66" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="J66" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K66" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L66" s="24"/>
+    </row>
+    <row r="67" spans="1:12" ht="105" x14ac:dyDescent="0.25">
+      <c r="A67" s="24"/>
+      <c r="B67" s="24"/>
+      <c r="C67" s="24"/>
+      <c r="D67" s="24"/>
+      <c r="E67" s="24"/>
+      <c r="F67" s="4">
+        <v>5</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L67" s="24"/>
+    </row>
+    <row r="68" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A68" s="25"/>
+      <c r="B68" s="25"/>
+      <c r="C68" s="25"/>
+      <c r="D68" s="25"/>
+      <c r="E68" s="25"/>
+      <c r="F68" s="4">
+        <v>6</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I68" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="J68" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K68" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L68" s="25"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="20"/>
+      <c r="B69" s="21"/>
+      <c r="C69" s="21"/>
+      <c r="D69" s="21"/>
+      <c r="E69" s="21"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="21"/>
+      <c r="H69" s="21"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="21"/>
+      <c r="K69" s="21"/>
+      <c r="L69" s="22"/>
+    </row>
+    <row r="70" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A70" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C70" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="D70" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="E70" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="F70" s="4">
+        <v>1</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I70" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L70" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="24"/>
+      <c r="B71" s="24"/>
+      <c r="C71" s="24"/>
+      <c r="D71" s="24"/>
+      <c r="E71" s="24"/>
+      <c r="F71" s="4">
+        <v>2</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I71" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="J71" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L71" s="24"/>
+    </row>
+    <row r="72" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A72" s="24"/>
+      <c r="B72" s="24"/>
+      <c r="C72" s="24"/>
+      <c r="D72" s="24"/>
+      <c r="E72" s="24"/>
+      <c r="F72" s="4">
+        <v>3</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="I72" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="J72" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K72" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="24"/>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A73" s="24"/>
+      <c r="B73" s="24"/>
+      <c r="C73" s="24"/>
+      <c r="D73" s="24"/>
+      <c r="E73" s="24"/>
+      <c r="F73" s="4">
+        <v>4</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="I73" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="J73" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K73" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L73" s="24"/>
+    </row>
+    <row r="74" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A74" s="24"/>
+      <c r="B74" s="24"/>
+      <c r="C74" s="24"/>
+      <c r="D74" s="24"/>
+      <c r="E74" s="24"/>
+      <c r="F74" s="4">
+        <v>5</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I74" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L74" s="24"/>
+    </row>
+    <row r="75" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A75" s="24"/>
+      <c r="B75" s="24"/>
+      <c r="C75" s="24"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="4">
+        <v>6</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I75" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="J75" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K75" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L75" s="24"/>
+    </row>
+    <row r="76" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A76" s="25"/>
+      <c r="B76" s="25"/>
+      <c r="C76" s="25"/>
+      <c r="D76" s="25"/>
+      <c r="E76" s="25"/>
+      <c r="F76" s="4">
+        <v>7</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I76" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="J76" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K76" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L76" s="25"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="77">
+    <mergeCell ref="A63:A68"/>
+    <mergeCell ref="L63:L68"/>
+    <mergeCell ref="E63:E68"/>
+    <mergeCell ref="D63:D68"/>
+    <mergeCell ref="C63:C68"/>
+    <mergeCell ref="B63:B68"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="A56:L56"/>
+    <mergeCell ref="A16:L16"/>
+    <mergeCell ref="A43:L43"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="L17:L22"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="B30:B35"/>
+    <mergeCell ref="C30:C35"/>
+    <mergeCell ref="D30:D35"/>
     <mergeCell ref="A1:L1"/>
+    <mergeCell ref="L3:L8"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="C3:C8"/>
+    <mergeCell ref="D3:D8"/>
+    <mergeCell ref="E3:E8"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="L10:L15"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="C17:C22"/>
+    <mergeCell ref="D17:D22"/>
+    <mergeCell ref="E17:E22"/>
+    <mergeCell ref="E44:E49"/>
+    <mergeCell ref="D44:D49"/>
+    <mergeCell ref="C44:C49"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="L24:L28"/>
+    <mergeCell ref="L30:L35"/>
+    <mergeCell ref="L37:L42"/>
+    <mergeCell ref="L44:L49"/>
+    <mergeCell ref="L57:L61"/>
+    <mergeCell ref="A29:L29"/>
+    <mergeCell ref="B44:B49"/>
+    <mergeCell ref="A44:A49"/>
+    <mergeCell ref="D37:D42"/>
+    <mergeCell ref="C37:C42"/>
+    <mergeCell ref="B37:B42"/>
+    <mergeCell ref="A37:A42"/>
+    <mergeCell ref="E30:E35"/>
+    <mergeCell ref="E37:E42"/>
+    <mergeCell ref="E57:E61"/>
+    <mergeCell ref="D57:D61"/>
+    <mergeCell ref="A69:L69"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="E70:E76"/>
+    <mergeCell ref="D70:D76"/>
+    <mergeCell ref="C70:C76"/>
+    <mergeCell ref="B70:B76"/>
+    <mergeCell ref="A70:A76"/>
+    <mergeCell ref="L70:L76"/>
+    <mergeCell ref="L51:L55"/>
+    <mergeCell ref="E51:E55"/>
+    <mergeCell ref="D51:D55"/>
+    <mergeCell ref="C51:C55"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="C57:C61"/>
+    <mergeCell ref="A62:L62"/>
   </mergeCells>
+  <conditionalFormatting sqref="K1:K49 K51:K68 K70:K1048576">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>"Pass"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Fail"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="H3" r:id="rId1" xr:uid="{98A392B9-FFF9-405C-B695-FBFC1336656F}"/>
+    <hyperlink ref="H10" r:id="rId2" xr:uid="{34770228-C043-47C3-BBAA-19D62DE91287}"/>
+    <hyperlink ref="H17" r:id="rId3" xr:uid="{4369EFA7-2985-44AA-9F69-009D0F86E7F7}"/>
+    <hyperlink ref="H24" r:id="rId4" xr:uid="{72BFBB62-6A32-4390-9BFF-D0B7A3CF79C1}"/>
+    <hyperlink ref="H30" r:id="rId5" xr:uid="{17AAFBB8-76CC-4AB5-AF48-2E8A0B7235A7}"/>
+    <hyperlink ref="H37" r:id="rId6" xr:uid="{E0F5479A-9665-470D-94F1-5988739028AB}"/>
+    <hyperlink ref="H44" r:id="rId7" xr:uid="{7686A3AA-8949-4191-BA82-9C07E295A5FC}"/>
+    <hyperlink ref="H63" r:id="rId8" xr:uid="{DAB1217A-AA3B-43BB-AF54-585F6CE0A056}"/>
+    <hyperlink ref="H51" r:id="rId9" xr:uid="{EDC0A092-6534-4668-B1E2-60705090BC74}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7727A5CD-B03E-4D3F-8D71-1F972933016E}">
-          <x14:formula1>
-            <xm:f>Sheet2!C1:C4</xm:f>
-          </x14:formula1>
-          <xm:sqref>J3:K200</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
 </worksheet>
 </file>
 

--- a/Manual-Testing/04_Test_Cases/Test_Cases_OrangeHRM.xlsx
+++ b/Manual-Testing/04_Test_Cases/Test_Cases_OrangeHRM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Testing\OrangeHRM-QA-Project\Manual-Testing\04_Test_Cases\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{974E3A6F-8DD0-4346-8AA1-3AE67CF8CB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF6140E-C662-426D-9322-85121EDDFF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" xr2:uid="{75FEA98A-859C-4F7D-ACE4-5329782BB20B}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="221">
   <si>
     <t>Test Case Description</t>
   </si>
@@ -496,27 +496,15 @@
     <t>TS_PIM_001</t>
   </si>
   <si>
-    <t>Verify admin can add employee successfully</t>
-  </si>
-  <si>
     <t>Admin logged in and on PIM page</t>
   </si>
   <si>
-    <t>Navigate to PIMmodule and click "Add employee" button</t>
-  </si>
-  <si>
     <t>employee created successfully and user should be navigated to employee information page</t>
   </si>
   <si>
     <t xml:space="preserve">Employee Information page url should contain "/viewPersonalDetails" </t>
   </si>
   <si>
-    <t>verify employee name displayed correctly</t>
-  </si>
-  <si>
-    <t>Employee details should match entered data</t>
-  </si>
-  <si>
     <t>Bug</t>
   </si>
   <si>
@@ -524,6 +512,183 @@
   </si>
   <si>
     <t>TC_Login_010</t>
+  </si>
+  <si>
+    <t>TC_PIM_002</t>
+  </si>
+  <si>
+    <t>Navigate to PIM module and click "Add employee" button</t>
+  </si>
+  <si>
+    <t>Leave mandatory fileds empty</t>
+  </si>
+  <si>
+    <t>"Required" validation messge should be displayed for mandatory fields.</t>
+  </si>
+  <si>
+    <t>Add employee page should be displayed</t>
+  </si>
+  <si>
+    <t>name fileds should be empty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify admin can add employee successfully </t>
+  </si>
+  <si>
+    <t>Verify admin can add employeewith empty Mandatory Fields</t>
+  </si>
+  <si>
+    <t>TC_PIM_003</t>
+  </si>
+  <si>
+    <t>TS_PIM_002</t>
+  </si>
+  <si>
+    <t>Navigate to PIM module and click "Employee List" button</t>
+  </si>
+  <si>
+    <t>click search button</t>
+  </si>
+  <si>
+    <t>Verify employee details in the below result table</t>
+  </si>
+  <si>
+    <t>BugHunter QA7</t>
+  </si>
+  <si>
+    <t>Emplyee search page should be displayed</t>
+  </si>
+  <si>
+    <t>employee name should be accepted</t>
+  </si>
+  <si>
+    <t>employee name should be accepted and displayed in the field</t>
+  </si>
+  <si>
+    <t>Matching employee record should be displayed in the below result table</t>
+  </si>
+  <si>
+    <t>correct employee record should be displayed</t>
+  </si>
+  <si>
+    <t>Verify admin can search existing Employee record</t>
+  </si>
+  <si>
+    <t>TC_PIM_004</t>
+  </si>
+  <si>
+    <t>Verify admin can search non-existing employee record</t>
+  </si>
+  <si>
+    <t>Enter valid employee name in the employee search field</t>
+  </si>
+  <si>
+    <t>Enter invalid employee name in the employee search field</t>
+  </si>
+  <si>
+    <t>wrong employee</t>
+  </si>
+  <si>
+    <t>"No Records Found" message should be displayed</t>
+  </si>
+  <si>
+    <t>name should be accepted</t>
+  </si>
+  <si>
+    <t>TC_PIM_005</t>
+  </si>
+  <si>
+    <t>TS_PIM_003</t>
+  </si>
+  <si>
+    <t>Verify admin can edit employee details</t>
+  </si>
+  <si>
+    <t>BUgHUntur QA7</t>
+  </si>
+  <si>
+    <t>employee record should be displayed</t>
+  </si>
+  <si>
+    <t>Enter existing employee name in the search field</t>
+  </si>
+  <si>
+    <t>click employee edit button</t>
+  </si>
+  <si>
+    <t>employee edit page should be opened</t>
+  </si>
+  <si>
+    <t>modify employee last name</t>
+  </si>
+  <si>
+    <t>QA007</t>
+  </si>
+  <si>
+    <t>new last name should be accepted</t>
+  </si>
+  <si>
+    <t>changes should be saved successfully</t>
+  </si>
+  <si>
+    <t>updated details should be displayed</t>
+  </si>
+  <si>
+    <t>Verify employee details</t>
+  </si>
+  <si>
+    <t>Veridy Admin can delete an existing employee</t>
+  </si>
+  <si>
+    <t>TS_PIM_004</t>
+  </si>
+  <si>
+    <t>TC_PIM_006</t>
+  </si>
+  <si>
+    <t>click employee delete button</t>
+  </si>
+  <si>
+    <t>click confirm delete from popup window</t>
+  </si>
+  <si>
+    <t>Verify employee is removed from list</t>
+  </si>
+  <si>
+    <t>BugHuntur QA7</t>
+  </si>
+  <si>
+    <t>Employee record should not appear in results</t>
+  </si>
+  <si>
+    <t>Employee record should be deleted successfully</t>
+  </si>
+  <si>
+    <t>Employee search page should be displayed</t>
+  </si>
+  <si>
+    <t>Confirmation popup should appear</t>
+  </si>
+  <si>
+    <t>Verify Admin can delete an existing employee</t>
+  </si>
+  <si>
+    <t>TC_PIM_007</t>
+  </si>
+  <si>
+    <t>click cancle from popup</t>
+  </si>
+  <si>
+    <t>Bug Huntur</t>
+  </si>
+  <si>
+    <t>Verify employee still exists in the result table</t>
+  </si>
+  <si>
+    <t>Employee should still be present</t>
+  </si>
+  <si>
+    <t>Employee should not be deleted</t>
   </si>
 </sst>
 </file>
@@ -778,15 +943,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -802,11 +958,17 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -817,7 +979,10 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1183,7 +1348,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74709E7A-6F17-4BAA-85D6-5A1E2510EB4F}">
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -1202,20 +1367,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="30"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
+      <c r="B1" s="29"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="30"/>
     </row>
     <row r="2" spans="1:12" ht="18" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -1256,19 +1421,19 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="20" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="20" t="s">
         <v>117</v>
       </c>
       <c r="F3" s="15">
@@ -1289,16 +1454,16 @@
       <c r="K3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="23" t="s">
+      <c r="L3" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="24"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
       <c r="F4" s="4">
         <v>2</v>
       </c>
@@ -1317,14 +1482,14 @@
       <c r="K4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="24"/>
+      <c r="L4" s="21"/>
     </row>
     <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
       <c r="F5" s="4">
         <v>3</v>
       </c>
@@ -1343,14 +1508,14 @@
       <c r="K5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L5" s="24"/>
+      <c r="L5" s="21"/>
     </row>
     <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
+      <c r="A6" s="21"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
+      <c r="E6" s="21"/>
       <c r="F6" s="4">
         <v>4</v>
       </c>
@@ -1369,14 +1534,14 @@
       <c r="K6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L6" s="24"/>
+      <c r="L6" s="21"/>
     </row>
     <row r="7" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
-      <c r="C7" s="24"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
       <c r="F7" s="4">
         <v>5</v>
       </c>
@@ -1395,14 +1560,14 @@
       <c r="K7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L7" s="24"/>
+      <c r="L7" s="21"/>
     </row>
     <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
-      <c r="E8" s="25"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
       <c r="F8" s="4">
         <v>6</v>
       </c>
@@ -1421,36 +1586,36 @@
       <c r="K8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L8" s="25"/>
+      <c r="L8" s="22"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
     </row>
     <row r="10" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="23" t="s">
+      <c r="E10" s="20" t="s">
         <v>117</v>
       </c>
       <c r="F10" s="11">
@@ -1471,16 +1636,16 @@
       <c r="K10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="23" t="s">
+      <c r="L10" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
+      <c r="D11" s="21"/>
+      <c r="E11" s="21"/>
       <c r="F11" s="11">
         <v>2</v>
       </c>
@@ -1499,14 +1664,14 @@
       <c r="K11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L11" s="24"/>
+      <c r="L11" s="21"/>
     </row>
     <row r="12" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
       <c r="F12" s="4">
         <v>3</v>
       </c>
@@ -1525,14 +1690,14 @@
       <c r="K12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L12" s="24"/>
+      <c r="L12" s="21"/>
     </row>
     <row r="13" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
       <c r="F13" s="4">
         <v>4</v>
       </c>
@@ -1551,14 +1716,14 @@
       <c r="K13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L13" s="24"/>
+      <c r="L13" s="21"/>
     </row>
     <row r="14" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="4">
         <v>5</v>
       </c>
@@ -1577,14 +1742,14 @@
       <c r="K14" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="24"/>
+      <c r="L14" s="21"/>
     </row>
     <row r="15" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A15" s="25"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="4">
         <v>6</v>
       </c>
@@ -1603,36 +1768,36 @@
       <c r="K15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="25"/>
+      <c r="L15" s="22"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="26"/>
-      <c r="D16" s="26"/>
-      <c r="E16" s="26"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="26"/>
-      <c r="H16" s="26"/>
-      <c r="I16" s="26"/>
-      <c r="J16" s="26"/>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
+      <c r="A16" s="23"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="23"/>
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+      <c r="L16" s="23"/>
     </row>
     <row r="17" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="23" t="s">
+      <c r="B17" s="20" t="s">
         <v>149</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E17" s="23" t="s">
+      <c r="E17" s="20" t="s">
         <v>117</v>
       </c>
       <c r="F17" s="4">
@@ -1653,16 +1818,16 @@
       <c r="K17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="23" t="s">
+      <c r="L17" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
       <c r="F18" s="4">
         <v>2</v>
       </c>
@@ -1681,14 +1846,14 @@
       <c r="K18" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L18" s="24"/>
+      <c r="L18" s="21"/>
     </row>
     <row r="19" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="24"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="21"/>
+      <c r="D19" s="21"/>
+      <c r="E19" s="21"/>
       <c r="F19" s="4">
         <v>3</v>
       </c>
@@ -1707,14 +1872,14 @@
       <c r="K19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L19" s="24"/>
+      <c r="L19" s="21"/>
     </row>
     <row r="20" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="24"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
       <c r="F20" s="4">
         <v>4</v>
       </c>
@@ -1733,14 +1898,14 @@
       <c r="K20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L20" s="24"/>
+      <c r="L20" s="21"/>
     </row>
     <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A21" s="24"/>
-      <c r="B21" s="24"/>
-      <c r="C21" s="24"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
       <c r="F21" s="4">
         <v>5</v>
       </c>
@@ -1759,14 +1924,14 @@
       <c r="K21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="24"/>
+      <c r="L21" s="21"/>
     </row>
     <row r="22" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A22" s="25"/>
-      <c r="B22" s="25"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="25"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
       <c r="F22" s="4">
         <v>6</v>
       </c>
@@ -1785,36 +1950,36 @@
       <c r="K22" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="25"/>
+      <c r="L22" s="22"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" s="20"/>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="21"/>
-      <c r="E23" s="21"/>
-      <c r="F23" s="33"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
-      <c r="J23" s="21"/>
-      <c r="K23" s="21"/>
-      <c r="L23" s="22"/>
+      <c r="A23" s="25"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="27"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="28"/>
     </row>
     <row r="24" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="23" t="s">
+      <c r="B24" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="C24" s="23" t="s">
+      <c r="C24" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="20" t="s">
         <v>117</v>
       </c>
       <c r="F24" s="4">
@@ -1835,16 +2000,16 @@
       <c r="K24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L24" s="23" t="s">
+      <c r="L24" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="24"/>
-      <c r="B25" s="24"/>
-      <c r="C25" s="24"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="24"/>
+      <c r="A25" s="21"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
       <c r="F25" s="4">
         <v>2</v>
       </c>
@@ -1863,14 +2028,14 @@
       <c r="K25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L25" s="24"/>
+      <c r="L25" s="21"/>
     </row>
     <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="24"/>
-      <c r="B26" s="24"/>
-      <c r="C26" s="24"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="24"/>
+      <c r="A26" s="21"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
       <c r="F26" s="4">
         <v>3</v>
       </c>
@@ -1889,14 +2054,14 @@
       <c r="K26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L26" s="24"/>
+      <c r="L26" s="21"/>
     </row>
     <row r="27" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="24"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="24"/>
+      <c r="A27" s="21"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
       <c r="F27" s="4">
         <v>4</v>
       </c>
@@ -1915,14 +2080,14 @@
       <c r="K27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="24"/>
+      <c r="L27" s="21"/>
     </row>
     <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="25"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="25"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
       <c r="F28" s="4">
         <v>5</v>
       </c>
@@ -1941,36 +2106,36 @@
       <c r="K28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L28" s="25"/>
+      <c r="L28" s="22"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A29" s="26"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="26"/>
-      <c r="D29" s="26"/>
-      <c r="E29" s="26"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="26"/>
-      <c r="H29" s="26"/>
-      <c r="I29" s="26"/>
-      <c r="J29" s="26"/>
-      <c r="K29" s="26"/>
-      <c r="L29" s="26"/>
+      <c r="A29" s="23"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="23"/>
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+      <c r="L29" s="23"/>
     </row>
     <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="20" t="s">
         <v>117</v>
       </c>
       <c r="F30" s="4">
@@ -1991,16 +2156,16 @@
       <c r="K30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L30" s="23" t="s">
+      <c r="L30" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="24"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="24"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="24"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
       <c r="F31" s="4">
         <v>2</v>
       </c>
@@ -2019,14 +2184,14 @@
       <c r="K31" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L31" s="24"/>
+      <c r="L31" s="21"/>
     </row>
     <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="24"/>
-      <c r="B32" s="24"/>
-      <c r="C32" s="24"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="24"/>
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
       <c r="F32" s="4">
         <v>3</v>
       </c>
@@ -2045,14 +2210,14 @@
       <c r="K32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L32" s="24"/>
+      <c r="L32" s="21"/>
     </row>
     <row r="33" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="24"/>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
       <c r="F33" s="4">
         <v>4</v>
       </c>
@@ -2071,14 +2236,14 @@
       <c r="K33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="24"/>
+      <c r="L33" s="21"/>
     </row>
     <row r="34" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A34" s="24"/>
-      <c r="B34" s="24"/>
-      <c r="C34" s="24"/>
-      <c r="D34" s="24"/>
-      <c r="E34" s="24"/>
+      <c r="A34" s="21"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="21"/>
+      <c r="D34" s="21"/>
+      <c r="E34" s="21"/>
       <c r="F34" s="4">
         <v>5</v>
       </c>
@@ -2097,14 +2262,14 @@
       <c r="K34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L34" s="24"/>
+      <c r="L34" s="21"/>
     </row>
     <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="25"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="25"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
       <c r="F35" s="4">
         <v>6</v>
       </c>
@@ -2123,36 +2288,36 @@
       <c r="K35" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L35" s="25"/>
+      <c r="L35" s="22"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="26"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
-      <c r="D36" s="26"/>
-      <c r="E36" s="26"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="26"/>
-      <c r="H36" s="26"/>
-      <c r="I36" s="26"/>
-      <c r="J36" s="26"/>
-      <c r="K36" s="26"/>
-      <c r="L36" s="26"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="23"/>
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
+      <c r="L36" s="23"/>
     </row>
     <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A37" s="23" t="s">
+      <c r="A37" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B37" s="23" t="s">
+      <c r="B37" s="20" t="s">
         <v>150</v>
       </c>
-      <c r="C37" s="23" t="s">
+      <c r="C37" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D37" s="23" t="s">
+      <c r="D37" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="E37" s="23" t="s">
+      <c r="E37" s="20" t="s">
         <v>117</v>
       </c>
       <c r="F37" s="4">
@@ -2173,16 +2338,16 @@
       <c r="K37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L37" s="23" t="s">
+      <c r="L37" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="24"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
+      <c r="A38" s="21"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="21"/>
+      <c r="D38" s="21"/>
+      <c r="E38" s="21"/>
       <c r="F38" s="4">
         <v>2</v>
       </c>
@@ -2201,14 +2366,14 @@
       <c r="K38" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L38" s="24"/>
+      <c r="L38" s="21"/>
     </row>
     <row r="39" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21"/>
+      <c r="D39" s="21"/>
+      <c r="E39" s="21"/>
       <c r="F39" s="4">
         <v>3</v>
       </c>
@@ -2227,14 +2392,14 @@
       <c r="K39" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L39" s="24"/>
+      <c r="L39" s="21"/>
     </row>
     <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="24"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="21"/>
       <c r="F40" s="4">
         <v>4</v>
       </c>
@@ -2253,14 +2418,14 @@
       <c r="K40" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L40" s="24"/>
+      <c r="L40" s="21"/>
     </row>
     <row r="41" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="24"/>
-      <c r="B41" s="24"/>
-      <c r="C41" s="24"/>
-      <c r="D41" s="24"/>
-      <c r="E41" s="24"/>
+      <c r="A41" s="21"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21"/>
+      <c r="D41" s="21"/>
+      <c r="E41" s="21"/>
       <c r="F41" s="4">
         <v>5</v>
       </c>
@@ -2279,14 +2444,14 @@
       <c r="K41" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L41" s="24"/>
+      <c r="L41" s="21"/>
     </row>
     <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="25"/>
-      <c r="B42" s="25"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="25"/>
-      <c r="E42" s="25"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
       <c r="F42" s="4">
         <v>6</v>
       </c>
@@ -2305,36 +2470,36 @@
       <c r="K42" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L42" s="25"/>
+      <c r="L42" s="22"/>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A43" s="26"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="26"/>
-      <c r="H43" s="26"/>
-      <c r="I43" s="26"/>
-      <c r="J43" s="26"/>
-      <c r="K43" s="26"/>
-      <c r="L43" s="26"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="23"/>
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+      <c r="L43" s="23"/>
     </row>
     <row r="44" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A44" s="23" t="s">
+      <c r="A44" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="B44" s="23" t="s">
+      <c r="B44" s="20" t="s">
         <v>151</v>
       </c>
-      <c r="C44" s="23" t="s">
+      <c r="C44" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D44" s="23" t="s">
+      <c r="D44" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="E44" s="23" t="s">
+      <c r="E44" s="20" t="s">
         <v>117</v>
       </c>
       <c r="F44" s="4">
@@ -2355,16 +2520,16 @@
       <c r="K44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="23" t="s">
+      <c r="L44" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="24"/>
-      <c r="B45" s="24"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="24"/>
-      <c r="E45" s="24"/>
+      <c r="A45" s="21"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="21"/>
+      <c r="D45" s="21"/>
+      <c r="E45" s="21"/>
       <c r="F45" s="4">
         <v>2</v>
       </c>
@@ -2383,14 +2548,14 @@
       <c r="K45" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="24"/>
+      <c r="L45" s="21"/>
     </row>
     <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="24"/>
-      <c r="B46" s="24"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="24"/>
-      <c r="E46" s="24"/>
+      <c r="A46" s="21"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="21"/>
+      <c r="D46" s="21"/>
+      <c r="E46" s="21"/>
       <c r="F46" s="4">
         <v>3</v>
       </c>
@@ -2409,14 +2574,14 @@
       <c r="K46" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L46" s="24"/>
+      <c r="L46" s="21"/>
     </row>
     <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="24"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="24"/>
-      <c r="D47" s="24"/>
-      <c r="E47" s="24"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="21"/>
+      <c r="E47" s="21"/>
       <c r="F47" s="4">
         <v>4</v>
       </c>
@@ -2435,14 +2600,14 @@
       <c r="K47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="24"/>
+      <c r="L47" s="21"/>
     </row>
     <row r="48" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A48" s="24"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="24"/>
-      <c r="D48" s="24"/>
-      <c r="E48" s="24"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="21"/>
+      <c r="D48" s="21"/>
+      <c r="E48" s="21"/>
       <c r="F48" s="4">
         <v>5</v>
       </c>
@@ -2461,14 +2626,14 @@
       <c r="K48" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L48" s="24"/>
+      <c r="L48" s="21"/>
     </row>
     <row r="49" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A49" s="25"/>
-      <c r="B49" s="25"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="25"/>
-      <c r="E49" s="25"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="22"/>
+      <c r="C49" s="22"/>
+      <c r="D49" s="22"/>
+      <c r="E49" s="22"/>
       <c r="F49" s="4">
         <v>6</v>
       </c>
@@ -2487,36 +2652,36 @@
       <c r="K49" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L49" s="25"/>
+      <c r="L49" s="22"/>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="20"/>
-      <c r="B50" s="21"/>
-      <c r="C50" s="21"/>
-      <c r="D50" s="21"/>
-      <c r="E50" s="21"/>
-      <c r="F50" s="21"/>
-      <c r="G50" s="21"/>
-      <c r="H50" s="21"/>
-      <c r="I50" s="21"/>
-      <c r="J50" s="21"/>
-      <c r="K50" s="21"/>
-      <c r="L50" s="22"/>
+      <c r="A50" s="25"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="26"/>
+      <c r="I50" s="26"/>
+      <c r="J50" s="26"/>
+      <c r="K50" s="26"/>
+      <c r="L50" s="28"/>
     </row>
     <row r="51" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="B51" s="23" t="s">
+      <c r="B51" s="20" t="s">
         <v>152</v>
       </c>
-      <c r="C51" s="23" t="s">
+      <c r="C51" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D51" s="23" t="s">
+      <c r="D51" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="E51" s="23" t="s">
+      <c r="E51" s="20" t="s">
         <v>140</v>
       </c>
       <c r="F51" s="4">
@@ -2537,16 +2702,16 @@
       <c r="K51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L51" s="23" t="s">
+      <c r="L51" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="24"/>
-      <c r="B52" s="24"/>
-      <c r="C52" s="24"/>
-      <c r="D52" s="24"/>
-      <c r="E52" s="24"/>
+      <c r="A52" s="21"/>
+      <c r="B52" s="21"/>
+      <c r="C52" s="21"/>
+      <c r="D52" s="21"/>
+      <c r="E52" s="21"/>
       <c r="F52" s="4">
         <v>2</v>
       </c>
@@ -2565,14 +2730,14 @@
       <c r="K52" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="24"/>
+      <c r="L52" s="21"/>
     </row>
     <row r="53" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="24"/>
-      <c r="B53" s="24"/>
-      <c r="C53" s="24"/>
-      <c r="D53" s="24"/>
-      <c r="E53" s="24"/>
+      <c r="A53" s="21"/>
+      <c r="B53" s="21"/>
+      <c r="C53" s="21"/>
+      <c r="D53" s="21"/>
+      <c r="E53" s="21"/>
       <c r="F53" s="4">
         <v>3</v>
       </c>
@@ -2591,14 +2756,14 @@
       <c r="K53" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L53" s="24"/>
+      <c r="L53" s="21"/>
     </row>
     <row r="54" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A54" s="24"/>
-      <c r="B54" s="24"/>
-      <c r="C54" s="24"/>
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
+      <c r="A54" s="21"/>
+      <c r="B54" s="21"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
       <c r="F54" s="4">
         <v>4</v>
       </c>
@@ -2617,14 +2782,14 @@
       <c r="K54" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L54" s="24"/>
+      <c r="L54" s="21"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="25"/>
-      <c r="B55" s="25"/>
-      <c r="C55" s="25"/>
-      <c r="D55" s="25"/>
-      <c r="E55" s="25"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
       <c r="F55" s="4">
         <v>5</v>
       </c>
@@ -2643,36 +2808,36 @@
       <c r="K55" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L55" s="25"/>
+      <c r="L55" s="22"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="26"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
-      <c r="D56" s="26"/>
-      <c r="E56" s="26"/>
-      <c r="F56" s="27"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="26"/>
-      <c r="I56" s="26"/>
-      <c r="J56" s="26"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="26"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
+      <c r="D56" s="23"/>
+      <c r="E56" s="23"/>
+      <c r="F56" s="24"/>
+      <c r="G56" s="23"/>
+      <c r="H56" s="23"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="23"/>
+      <c r="K56" s="23"/>
+      <c r="L56" s="23"/>
     </row>
     <row r="57" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A57" s="23" t="s">
+      <c r="A57" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="B57" s="23" t="s">
+      <c r="B57" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D57" s="23" t="s">
+      <c r="D57" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="E57" s="23" t="s">
+      <c r="E57" s="20" t="s">
         <v>110</v>
       </c>
       <c r="F57" s="4">
@@ -2693,16 +2858,16 @@
       <c r="K57" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L57" s="23" t="s">
+      <c r="L57" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="24"/>
-      <c r="B58" s="24"/>
-      <c r="C58" s="24"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="24"/>
+      <c r="A58" s="21"/>
+      <c r="B58" s="21"/>
+      <c r="C58" s="21"/>
+      <c r="D58" s="21"/>
+      <c r="E58" s="21"/>
       <c r="F58" s="4">
         <v>2</v>
       </c>
@@ -2721,14 +2886,14 @@
       <c r="K58" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L58" s="24"/>
+      <c r="L58" s="21"/>
     </row>
     <row r="59" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A59" s="24"/>
-      <c r="B59" s="24"/>
-      <c r="C59" s="24"/>
-      <c r="D59" s="24"/>
-      <c r="E59" s="24"/>
+      <c r="A59" s="21"/>
+      <c r="B59" s="21"/>
+      <c r="C59" s="21"/>
+      <c r="D59" s="21"/>
+      <c r="E59" s="21"/>
       <c r="F59" s="4">
         <v>3</v>
       </c>
@@ -2747,14 +2912,14 @@
       <c r="K59" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="24"/>
+      <c r="L59" s="21"/>
     </row>
     <row r="60" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A60" s="24"/>
-      <c r="B60" s="24"/>
-      <c r="C60" s="24"/>
-      <c r="D60" s="24"/>
-      <c r="E60" s="24"/>
+      <c r="A60" s="21"/>
+      <c r="B60" s="21"/>
+      <c r="C60" s="21"/>
+      <c r="D60" s="21"/>
+      <c r="E60" s="21"/>
       <c r="F60" s="4">
         <v>4</v>
       </c>
@@ -2773,14 +2938,14 @@
       <c r="K60" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L60" s="24"/>
+      <c r="L60" s="21"/>
     </row>
     <row r="61" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A61" s="25"/>
-      <c r="B61" s="25"/>
-      <c r="C61" s="25"/>
-      <c r="D61" s="25"/>
-      <c r="E61" s="25"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
       <c r="F61" s="4">
         <v>5</v>
       </c>
@@ -2799,36 +2964,36 @@
       <c r="K61" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L61" s="25"/>
+      <c r="L61" s="22"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="20"/>
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="21"/>
-      <c r="F62" s="33"/>
-      <c r="G62" s="21"/>
-      <c r="H62" s="21"/>
-      <c r="I62" s="21"/>
-      <c r="J62" s="21"/>
-      <c r="K62" s="21"/>
-      <c r="L62" s="22"/>
+      <c r="A62" s="25"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="27"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="26"/>
+      <c r="I62" s="26"/>
+      <c r="J62" s="26"/>
+      <c r="K62" s="26"/>
+      <c r="L62" s="28"/>
     </row>
     <row r="63" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A63" s="23" t="s">
-        <v>165</v>
-      </c>
-      <c r="B63" s="23" t="s">
+      <c r="A63" s="20" t="s">
+        <v>161</v>
+      </c>
+      <c r="B63" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="D63" s="23" t="s">
+      <c r="D63" s="20" t="s">
         <v>124</v>
       </c>
-      <c r="E63" s="23" t="s">
+      <c r="E63" s="20" t="s">
         <v>117</v>
       </c>
       <c r="F63" s="4">
@@ -2849,16 +3014,16 @@
       <c r="K63" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L63" s="23" t="s">
+      <c r="L63" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A64" s="24"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="24"/>
-      <c r="E64" s="24"/>
+      <c r="A64" s="21"/>
+      <c r="B64" s="21"/>
+      <c r="C64" s="21"/>
+      <c r="D64" s="21"/>
+      <c r="E64" s="21"/>
       <c r="F64" s="4">
         <v>2</v>
       </c>
@@ -2877,14 +3042,14 @@
       <c r="K64" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L64" s="24"/>
+      <c r="L64" s="21"/>
     </row>
     <row r="65" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A65" s="24"/>
-      <c r="B65" s="24"/>
-      <c r="C65" s="24"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24"/>
+      <c r="A65" s="21"/>
+      <c r="B65" s="21"/>
+      <c r="C65" s="21"/>
+      <c r="D65" s="21"/>
+      <c r="E65" s="21"/>
       <c r="F65" s="4">
         <v>3</v>
       </c>
@@ -2903,14 +3068,14 @@
       <c r="K65" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L65" s="24"/>
+      <c r="L65" s="21"/>
     </row>
     <row r="66" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A66" s="24"/>
-      <c r="B66" s="24"/>
-      <c r="C66" s="24"/>
-      <c r="D66" s="24"/>
-      <c r="E66" s="24"/>
+      <c r="A66" s="21"/>
+      <c r="B66" s="21"/>
+      <c r="C66" s="21"/>
+      <c r="D66" s="21"/>
+      <c r="E66" s="21"/>
       <c r="F66" s="4">
         <v>4</v>
       </c>
@@ -2929,14 +3094,14 @@
       <c r="K66" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L66" s="24"/>
+      <c r="L66" s="21"/>
     </row>
     <row r="67" spans="1:12" ht="105" x14ac:dyDescent="0.25">
-      <c r="A67" s="24"/>
-      <c r="B67" s="24"/>
-      <c r="C67" s="24"/>
-      <c r="D67" s="24"/>
-      <c r="E67" s="24"/>
+      <c r="A67" s="21"/>
+      <c r="B67" s="21"/>
+      <c r="C67" s="21"/>
+      <c r="D67" s="21"/>
+      <c r="E67" s="21"/>
       <c r="F67" s="4">
         <v>5</v>
       </c>
@@ -2955,14 +3120,14 @@
       <c r="K67" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="L67" s="24"/>
+      <c r="L67" s="21"/>
     </row>
     <row r="68" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A68" s="25"/>
-      <c r="B68" s="25"/>
-      <c r="C68" s="25"/>
-      <c r="D68" s="25"/>
-      <c r="E68" s="25"/>
+      <c r="A68" s="22"/>
+      <c r="B68" s="22"/>
+      <c r="C68" s="22"/>
+      <c r="D68" s="22"/>
+      <c r="E68" s="22"/>
       <c r="F68" s="4">
         <v>6</v>
       </c>
@@ -2981,43 +3146,43 @@
       <c r="K68" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L68" s="25"/>
+      <c r="L68" s="22"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="20"/>
-      <c r="B69" s="21"/>
-      <c r="C69" s="21"/>
-      <c r="D69" s="21"/>
-      <c r="E69" s="21"/>
-      <c r="F69" s="21"/>
-      <c r="G69" s="21"/>
-      <c r="H69" s="21"/>
-      <c r="I69" s="21"/>
-      <c r="J69" s="21"/>
-      <c r="K69" s="21"/>
-      <c r="L69" s="22"/>
+      <c r="A69" s="25"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="26"/>
+      <c r="L69" s="28"/>
     </row>
     <row r="70" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A70" s="23" t="s">
+      <c r="A70" s="20" t="s">
         <v>127</v>
       </c>
-      <c r="B70" s="23" t="s">
+      <c r="B70" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="23" t="s">
+      <c r="D70" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="E70" s="20" t="s">
         <v>156</v>
-      </c>
-      <c r="E70" s="23" t="s">
-        <v>157</v>
       </c>
       <c r="F70" s="4">
         <v>1</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>17</v>
@@ -3031,16 +3196,16 @@
       <c r="K70" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L70" s="23" t="s">
+      <c r="L70" s="20" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="24"/>
-      <c r="B71" s="24"/>
-      <c r="C71" s="24"/>
-      <c r="D71" s="24"/>
-      <c r="E71" s="24"/>
+      <c r="A71" s="21"/>
+      <c r="B71" s="21"/>
+      <c r="C71" s="21"/>
+      <c r="D71" s="21"/>
+      <c r="E71" s="21"/>
       <c r="F71" s="4">
         <v>2</v>
       </c>
@@ -3048,7 +3213,7 @@
         <v>129</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="I71" s="5" t="s">
         <v>134</v>
@@ -3059,14 +3224,14 @@
       <c r="K71" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L71" s="24"/>
+      <c r="L71" s="21"/>
     </row>
     <row r="72" spans="1:12" ht="30" x14ac:dyDescent="0.25">
-      <c r="A72" s="24"/>
-      <c r="B72" s="24"/>
-      <c r="C72" s="24"/>
-      <c r="D72" s="24"/>
-      <c r="E72" s="24"/>
+      <c r="A72" s="21"/>
+      <c r="B72" s="21"/>
+      <c r="C72" s="21"/>
+      <c r="D72" s="21"/>
+      <c r="E72" s="21"/>
       <c r="F72" s="4">
         <v>3</v>
       </c>
@@ -3074,7 +3239,7 @@
         <v>130</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="I72" s="5" t="s">
         <v>135</v>
@@ -3085,14 +3250,14 @@
       <c r="K72" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L72" s="24"/>
+      <c r="L72" s="21"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="24"/>
-      <c r="B73" s="24"/>
-      <c r="C73" s="24"/>
-      <c r="D73" s="24"/>
-      <c r="E73" s="24"/>
+      <c r="A73" s="21"/>
+      <c r="B73" s="21"/>
+      <c r="C73" s="21"/>
+      <c r="D73" s="21"/>
+      <c r="E73" s="21"/>
       <c r="F73" s="4">
         <v>4</v>
       </c>
@@ -3111,14 +3276,14 @@
       <c r="K73" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L73" s="24"/>
+      <c r="L73" s="21"/>
     </row>
     <row r="74" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A74" s="24"/>
-      <c r="B74" s="24"/>
-      <c r="C74" s="24"/>
-      <c r="D74" s="24"/>
-      <c r="E74" s="24"/>
+      <c r="A74" s="21"/>
+      <c r="B74" s="21"/>
+      <c r="C74" s="21"/>
+      <c r="D74" s="21"/>
+      <c r="E74" s="21"/>
       <c r="F74" s="4">
         <v>5</v>
       </c>
@@ -3129,7 +3294,7 @@
         <v>17</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="J74" s="1" t="s">
         <v>33</v>
@@ -3137,14 +3302,14 @@
       <c r="K74" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L74" s="24"/>
+      <c r="L74" s="21"/>
     </row>
     <row r="75" spans="1:12" ht="45" x14ac:dyDescent="0.25">
-      <c r="A75" s="24"/>
-      <c r="B75" s="24"/>
-      <c r="C75" s="24"/>
-      <c r="D75" s="24"/>
-      <c r="E75" s="24"/>
+      <c r="A75" s="21"/>
+      <c r="B75" s="21"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="21"/>
       <c r="F75" s="4">
         <v>6</v>
       </c>
@@ -3155,7 +3320,7 @@
         <v>17</v>
       </c>
       <c r="I75" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>33</v>
@@ -3163,49 +3328,994 @@
       <c r="K75" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L75" s="24"/>
-    </row>
-    <row r="76" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="L75" s="21"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="25"/>
-      <c r="B76" s="25"/>
-      <c r="C76" s="25"/>
-      <c r="D76" s="25"/>
-      <c r="E76" s="25"/>
-      <c r="F76" s="4">
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="28"/>
+    </row>
+    <row r="77" spans="1:12" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B77" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="C77" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D77" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="E77" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F77" s="4">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I77" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="J77" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K77" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L77" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="21"/>
+      <c r="B78" s="21"/>
+      <c r="C78" s="21"/>
+      <c r="D78" s="21"/>
+      <c r="E78" s="21"/>
+      <c r="F78" s="4">
+        <v>2</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I78" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="J78" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K78" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L78" s="21"/>
+    </row>
+    <row r="79" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A79" s="22"/>
+      <c r="B79" s="22"/>
+      <c r="C79" s="22"/>
+      <c r="D79" s="22"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="4">
+        <v>3</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I79" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="J79" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K79" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L79" s="22"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="25"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="28"/>
+    </row>
+    <row r="81" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A81" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="B81" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C81" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D81" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="E81" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F81" s="4">
+        <v>1</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I81" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A82" s="21"/>
+      <c r="B82" s="21"/>
+      <c r="C82" s="21"/>
+      <c r="D82" s="21"/>
+      <c r="E82" s="21"/>
+      <c r="F82" s="4">
+        <v>2</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I82" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L82" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A83" s="21"/>
+      <c r="B83" s="21"/>
+      <c r="C83" s="21"/>
+      <c r="D83" s="21"/>
+      <c r="E83" s="21"/>
+      <c r="F83" s="4">
+        <v>3</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I83" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A84" s="22"/>
+      <c r="B84" s="22"/>
+      <c r="C84" s="22"/>
+      <c r="D84" s="22"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="4">
+        <v>4</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I84" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A85" s="25"/>
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="26"/>
+      <c r="K85" s="26"/>
+      <c r="L85" s="28"/>
+    </row>
+    <row r="86" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A86" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="B86" s="20" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D86" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="E86" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F86" s="4">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J86" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K86" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L86" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A87" s="21"/>
+      <c r="B87" s="21"/>
+      <c r="C87" s="21"/>
+      <c r="D87" s="21"/>
+      <c r="E87" s="21"/>
+      <c r="F87" s="4">
+        <v>2</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="J87" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K87" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L87" s="21"/>
+    </row>
+    <row r="88" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A88" s="22"/>
+      <c r="B88" s="22"/>
+      <c r="C88" s="22"/>
+      <c r="D88" s="22"/>
+      <c r="E88" s="22"/>
+      <c r="F88" s="4">
+        <v>3</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I88" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="J88" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K88" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L88" s="22"/>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A89" s="25"/>
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="26"/>
+      <c r="G89" s="26"/>
+      <c r="H89" s="26"/>
+      <c r="I89" s="26"/>
+      <c r="J89" s="26"/>
+      <c r="K89" s="26"/>
+      <c r="L89" s="28"/>
+    </row>
+    <row r="90" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A90" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="B90" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="C90" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D90" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="E90" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F90" s="4">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I90" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J90" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K90" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L90" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A91" s="21"/>
+      <c r="B91" s="21"/>
+      <c r="C91" s="21"/>
+      <c r="D91" s="21"/>
+      <c r="E91" s="21"/>
+      <c r="F91" s="4">
+        <v>2</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="J91" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K91" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="21"/>
+    </row>
+    <row r="92" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A92" s="21"/>
+      <c r="B92" s="21"/>
+      <c r="C92" s="21"/>
+      <c r="D92" s="21"/>
+      <c r="E92" s="21"/>
+      <c r="F92" s="4">
+        <v>3</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="J92" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K92" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L92" s="21"/>
+    </row>
+    <row r="93" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A93" s="21"/>
+      <c r="B93" s="21"/>
+      <c r="C93" s="21"/>
+      <c r="D93" s="21"/>
+      <c r="E93" s="21"/>
+      <c r="F93" s="4">
+        <v>4</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I93" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="J93" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K93" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L93" s="21"/>
+    </row>
+    <row r="94" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A94" s="21"/>
+      <c r="B94" s="21"/>
+      <c r="C94" s="21"/>
+      <c r="D94" s="21"/>
+      <c r="E94" s="21"/>
+      <c r="F94" s="4">
+        <v>5</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="21"/>
+    </row>
+    <row r="95" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A95" s="21"/>
+      <c r="B95" s="21"/>
+      <c r="C95" s="21"/>
+      <c r="D95" s="21"/>
+      <c r="E95" s="21"/>
+      <c r="F95" s="4">
+        <v>6</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I95" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="J95" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L95" s="21"/>
+    </row>
+    <row r="96" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A96" s="22"/>
+      <c r="B96" s="22"/>
+      <c r="C96" s="22"/>
+      <c r="D96" s="22"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="4">
         <v>7</v>
       </c>
-      <c r="G76" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H76" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I76" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="J76" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="K76" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L76" s="25"/>
+      <c r="G96" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I96" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="J96" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K96" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="22"/>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A97" s="25"/>
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26"/>
+      <c r="H97" s="26"/>
+      <c r="I97" s="26"/>
+      <c r="J97" s="26"/>
+      <c r="K97" s="26"/>
+      <c r="L97" s="28"/>
+    </row>
+    <row r="98" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A98" s="20" t="s">
+        <v>205</v>
+      </c>
+      <c r="B98" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="C98" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D98" s="20" t="s">
+        <v>203</v>
+      </c>
+      <c r="E98" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F98" s="4">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K98" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L98" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A99" s="21"/>
+      <c r="B99" s="21"/>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="4">
+        <v>2</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="I99" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K99" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L99" s="21"/>
+    </row>
+    <row r="100" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A100" s="21"/>
+      <c r="B100" s="21"/>
+      <c r="C100" s="21"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="21"/>
+      <c r="F100" s="4">
+        <v>3</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I100" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K100" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="21"/>
+    </row>
+    <row r="101" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A101" s="21"/>
+      <c r="B101" s="21"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="21"/>
+      <c r="F101" s="4">
+        <v>4</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J101" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K101" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="21"/>
+    </row>
+    <row r="102" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A102" s="21"/>
+      <c r="B102" s="21"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="21"/>
+      <c r="F102" s="4">
+        <v>5</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I102" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="J102" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K102" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L102" s="21"/>
+    </row>
+    <row r="103" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A103" s="22"/>
+      <c r="B103" s="22"/>
+      <c r="C103" s="22"/>
+      <c r="D103" s="22"/>
+      <c r="E103" s="22"/>
+      <c r="F103" s="4">
+        <v>6</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I103" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="J103" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K103" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L103" s="22"/>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A104" s="25"/>
+      <c r="B104" s="26"/>
+      <c r="C104" s="26"/>
+      <c r="D104" s="26"/>
+      <c r="E104" s="26"/>
+      <c r="F104" s="26"/>
+      <c r="G104" s="26"/>
+      <c r="H104" s="26"/>
+      <c r="I104" s="26"/>
+      <c r="J104" s="26"/>
+      <c r="K104" s="26"/>
+      <c r="L104" s="28"/>
+    </row>
+    <row r="105" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A105" s="20" t="s">
+        <v>215</v>
+      </c>
+      <c r="B105" s="20" t="s">
+        <v>204</v>
+      </c>
+      <c r="C105" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="D105" s="20" t="s">
+        <v>214</v>
+      </c>
+      <c r="E105" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="F105" s="4">
+        <v>1</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I105" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="J105" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K105" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L105" s="20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A106" s="21"/>
+      <c r="B106" s="21"/>
+      <c r="C106" s="21"/>
+      <c r="D106" s="21"/>
+      <c r="E106" s="21"/>
+      <c r="F106" s="4">
+        <v>2</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="J106" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K106" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L106" s="21"/>
+    </row>
+    <row r="107" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+      <c r="A107" s="21"/>
+      <c r="B107" s="21"/>
+      <c r="C107" s="21"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="21"/>
+      <c r="F107" s="4">
+        <v>3</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I107" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="J107" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K107" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L107" s="21"/>
+    </row>
+    <row r="108" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A108" s="21"/>
+      <c r="B108" s="21"/>
+      <c r="C108" s="21"/>
+      <c r="D108" s="21"/>
+      <c r="E108" s="21"/>
+      <c r="F108" s="4">
+        <v>4</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="J108" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K108" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L108" s="21"/>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A109" s="21"/>
+      <c r="B109" s="21"/>
+      <c r="C109" s="21"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="21"/>
+      <c r="F109" s="4">
+        <v>5</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="J109" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K109" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L109" s="21"/>
+    </row>
+    <row r="110" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+      <c r="A110" s="22"/>
+      <c r="B110" s="22"/>
+      <c r="C110" s="22"/>
+      <c r="D110" s="22"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="4">
+        <v>6</v>
+      </c>
+      <c r="G110" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="J110" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K110" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L110" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="77">
-    <mergeCell ref="A63:A68"/>
-    <mergeCell ref="L63:L68"/>
-    <mergeCell ref="E63:E68"/>
-    <mergeCell ref="D63:D68"/>
-    <mergeCell ref="C63:C68"/>
-    <mergeCell ref="B63:B68"/>
-    <mergeCell ref="B57:B61"/>
-    <mergeCell ref="A57:A61"/>
-    <mergeCell ref="A36:L36"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="C24:C28"/>
-    <mergeCell ref="A56:L56"/>
+  <mergeCells count="118">
+    <mergeCell ref="A104:L104"/>
+    <mergeCell ref="L105:L110"/>
+    <mergeCell ref="E105:E110"/>
+    <mergeCell ref="D105:D110"/>
+    <mergeCell ref="C105:C110"/>
+    <mergeCell ref="B105:B110"/>
+    <mergeCell ref="A105:A110"/>
+    <mergeCell ref="A97:L97"/>
+    <mergeCell ref="L98:L103"/>
+    <mergeCell ref="E98:E103"/>
+    <mergeCell ref="D98:D103"/>
+    <mergeCell ref="C98:C103"/>
+    <mergeCell ref="B98:B103"/>
+    <mergeCell ref="A98:A103"/>
+    <mergeCell ref="A85:L85"/>
+    <mergeCell ref="A80:L80"/>
+    <mergeCell ref="A89:L89"/>
+    <mergeCell ref="E90:E96"/>
+    <mergeCell ref="D90:D96"/>
+    <mergeCell ref="C90:C96"/>
+    <mergeCell ref="B90:B96"/>
+    <mergeCell ref="A90:A96"/>
+    <mergeCell ref="L90:L96"/>
+    <mergeCell ref="A81:A84"/>
+    <mergeCell ref="B81:B84"/>
+    <mergeCell ref="C81:C84"/>
+    <mergeCell ref="D81:D84"/>
+    <mergeCell ref="E81:E84"/>
+    <mergeCell ref="L86:L88"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="B86:B88"/>
+    <mergeCell ref="C86:C88"/>
+    <mergeCell ref="D86:D88"/>
+    <mergeCell ref="E86:E88"/>
+    <mergeCell ref="A76:L76"/>
+    <mergeCell ref="E77:E79"/>
+    <mergeCell ref="D77:D79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="L77:L79"/>
+    <mergeCell ref="L70:L75"/>
+    <mergeCell ref="L51:L55"/>
+    <mergeCell ref="E51:E55"/>
+    <mergeCell ref="D51:D55"/>
+    <mergeCell ref="C51:C55"/>
+    <mergeCell ref="C57:C61"/>
+    <mergeCell ref="A62:L62"/>
+    <mergeCell ref="E70:E75"/>
+    <mergeCell ref="D70:D75"/>
+    <mergeCell ref="C70:C75"/>
+    <mergeCell ref="B70:B75"/>
+    <mergeCell ref="A70:A75"/>
+    <mergeCell ref="E30:E35"/>
+    <mergeCell ref="E37:E42"/>
+    <mergeCell ref="E57:E61"/>
+    <mergeCell ref="D57:D61"/>
+    <mergeCell ref="A69:L69"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="A50:L50"/>
+    <mergeCell ref="B51:B55"/>
+    <mergeCell ref="A44:A49"/>
+    <mergeCell ref="D37:D42"/>
+    <mergeCell ref="C37:C42"/>
+    <mergeCell ref="B37:B42"/>
+    <mergeCell ref="A37:A42"/>
+    <mergeCell ref="A9:L9"/>
+    <mergeCell ref="A10:A15"/>
+    <mergeCell ref="B10:B15"/>
+    <mergeCell ref="C10:C15"/>
+    <mergeCell ref="D10:D15"/>
+    <mergeCell ref="E10:E15"/>
+    <mergeCell ref="L10:L15"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="L3:L8"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="B3:B8"/>
+    <mergeCell ref="C3:C8"/>
+    <mergeCell ref="D3:D8"/>
+    <mergeCell ref="E3:E8"/>
     <mergeCell ref="A16:L16"/>
     <mergeCell ref="A43:L43"/>
     <mergeCell ref="A23:L23"/>
@@ -3214,64 +4324,38 @@
     <mergeCell ref="B30:B35"/>
     <mergeCell ref="C30:C35"/>
     <mergeCell ref="D30:D35"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="L3:L8"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="B3:B8"/>
-    <mergeCell ref="C3:C8"/>
-    <mergeCell ref="D3:D8"/>
-    <mergeCell ref="E3:E8"/>
-    <mergeCell ref="A9:L9"/>
-    <mergeCell ref="A10:A15"/>
-    <mergeCell ref="B10:B15"/>
-    <mergeCell ref="C10:C15"/>
-    <mergeCell ref="D10:D15"/>
-    <mergeCell ref="E10:E15"/>
-    <mergeCell ref="L10:L15"/>
     <mergeCell ref="A17:A22"/>
     <mergeCell ref="B17:B22"/>
     <mergeCell ref="C17:C22"/>
     <mergeCell ref="D17:D22"/>
     <mergeCell ref="E17:E22"/>
+    <mergeCell ref="D24:D28"/>
+    <mergeCell ref="E24:E28"/>
+    <mergeCell ref="L24:L28"/>
+    <mergeCell ref="B57:B61"/>
+    <mergeCell ref="A57:A61"/>
+    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="C24:C28"/>
+    <mergeCell ref="A56:L56"/>
     <mergeCell ref="E44:E49"/>
     <mergeCell ref="D44:D49"/>
     <mergeCell ref="C44:C49"/>
-    <mergeCell ref="D24:D28"/>
-    <mergeCell ref="E24:E28"/>
-    <mergeCell ref="L24:L28"/>
     <mergeCell ref="L30:L35"/>
     <mergeCell ref="L37:L42"/>
     <mergeCell ref="L44:L49"/>
     <mergeCell ref="L57:L61"/>
     <mergeCell ref="A29:L29"/>
     <mergeCell ref="B44:B49"/>
-    <mergeCell ref="A44:A49"/>
-    <mergeCell ref="D37:D42"/>
-    <mergeCell ref="C37:C42"/>
-    <mergeCell ref="B37:B42"/>
-    <mergeCell ref="A37:A42"/>
-    <mergeCell ref="E30:E35"/>
-    <mergeCell ref="E37:E42"/>
-    <mergeCell ref="E57:E61"/>
-    <mergeCell ref="D57:D61"/>
-    <mergeCell ref="A69:L69"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="A50:L50"/>
-    <mergeCell ref="E70:E76"/>
-    <mergeCell ref="D70:D76"/>
-    <mergeCell ref="C70:C76"/>
-    <mergeCell ref="B70:B76"/>
-    <mergeCell ref="A70:A76"/>
-    <mergeCell ref="L70:L76"/>
-    <mergeCell ref="L51:L55"/>
-    <mergeCell ref="E51:E55"/>
-    <mergeCell ref="D51:D55"/>
-    <mergeCell ref="C51:C55"/>
-    <mergeCell ref="B51:B55"/>
-    <mergeCell ref="C57:C61"/>
-    <mergeCell ref="A62:L62"/>
+    <mergeCell ref="A63:A68"/>
+    <mergeCell ref="L63:L68"/>
+    <mergeCell ref="E63:E68"/>
+    <mergeCell ref="D63:D68"/>
+    <mergeCell ref="C63:C68"/>
+    <mergeCell ref="B63:B68"/>
   </mergeCells>
-  <conditionalFormatting sqref="K1:K49 K51:K68 K70:K1048576">
+  <conditionalFormatting sqref="K1:K49 K51:K68 K70:K75 K77:K79 K86:K88 K81:K84 K90:K96 K98:K103 K105:K1048576">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"Pass"</formula>
     </cfRule>
